--- a/bayes-yjx.xlsx
+++ b/bayes-yjx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansa1\OneDrive\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{724DE57C-F822-46B2-A144-B35A191F3E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C3410E3-C427-4B2F-9D6D-71B39AC7E667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="35">
   <si>
     <t>Year</t>
   </si>
@@ -99,6 +99,33 @@
   </si>
   <si>
     <t>Federal Reserve Economic Data series CPIAUCNS</t>
+  </si>
+  <si>
+    <t>International</t>
+  </si>
+  <si>
+    <t>Emerging</t>
+  </si>
+  <si>
+    <t>1970-2025</t>
+  </si>
+  <si>
+    <t>Novel Investor, taken from Morgan Stanley Capital International (MSCI)</t>
+  </si>
+  <si>
+    <t>12% Canada + 88% MSCI EAFE, arithmetic stock index returns, not in %</t>
+  </si>
+  <si>
+    <t>1988-2025</t>
+  </si>
+  <si>
+    <t>MSCI EM, arithmetic stock index annual returns, not in %</t>
+  </si>
+  <si>
+    <t>Developed non-US stock arithmetic nominal returns</t>
+  </si>
+  <si>
+    <t>Emerging stock arithmetic nominal returns</t>
   </si>
 </sst>
 </file>
@@ -108,7 +135,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -156,42 +183,6 @@
       <name val="Cambria"/>
       <family val="1"/>
       <charset val="204"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Cambria"/>
-      <family val="1"/>
-      <charset val="204"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Cambria"/>
-      <family val="1"/>
-      <charset val="204"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="Cambria"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="Cambria"/>
-      <family val="1"/>
     </font>
     <font>
       <sz val="14"/>
@@ -245,7 +236,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -273,60 +264,43 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -641,8 +615,8 @@
     <col min="3" max="3" width="18.5703125" style="2" customWidth="1"/>
     <col min="4" max="4" width="16" style="2" customWidth="1"/>
     <col min="5" max="5" width="19.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="14" style="15" customWidth="1"/>
-    <col min="7" max="7" width="21.85546875" style="13" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" style="10" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" style="2" customWidth="1"/>
     <col min="8" max="8" width="22.42578125" style="10" customWidth="1"/>
     <col min="9" max="9" width="16.42578125" style="2" customWidth="1"/>
     <col min="10" max="16384" width="9.140625" style="1"/>
@@ -664,8 +638,12 @@
       <c r="E1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="16"/>
-      <c r="G1" s="11"/>
+      <c r="F1" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="H1" s="8"/>
       <c r="I1" s="3"/>
     </row>
@@ -680,11 +658,10 @@
       <c r="D2" s="2">
         <v>0.77</v>
       </c>
-      <c r="E2" s="25">
+      <c r="E2" s="17">
         <v>17.3</v>
       </c>
-      <c r="F2" s="14"/>
-      <c r="G2" s="11"/>
+      <c r="F2" s="8"/>
       <c r="H2" s="8"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -700,11 +677,10 @@
       <c r="D3" s="2">
         <v>0.85</v>
       </c>
-      <c r="E3" s="25">
+      <c r="E3" s="17">
         <v>17.100000000000001</v>
       </c>
-      <c r="F3" s="14"/>
-      <c r="G3" s="11"/>
+      <c r="F3" s="8"/>
       <c r="H3" s="8"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -720,11 +696,10 @@
       <c r="D4" s="2">
         <v>0.97</v>
       </c>
-      <c r="E4" s="25">
+      <c r="E4" s="17">
         <v>17.2</v>
       </c>
-      <c r="F4" s="14"/>
-      <c r="G4" s="11"/>
+      <c r="F4" s="8"/>
       <c r="H4" s="8"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -740,11 +715,10 @@
       <c r="D5" s="2">
         <v>0.98</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="17">
         <v>16.100000000000001</v>
       </c>
-      <c r="F5" s="14"/>
-      <c r="G5" s="11"/>
+      <c r="F5" s="8"/>
       <c r="H5" s="8"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -760,11 +734,10 @@
       <c r="D6" s="2">
         <v>0.82</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="17">
         <v>14.6</v>
       </c>
-      <c r="F6" s="14"/>
-      <c r="G6" s="11"/>
+      <c r="F6" s="8"/>
       <c r="H6" s="8"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -780,11 +753,10 @@
       <c r="D7" s="2">
         <v>0.5</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="17">
         <v>13.1</v>
       </c>
-      <c r="F7" s="14"/>
-      <c r="G7" s="11"/>
+      <c r="F7" s="8"/>
       <c r="H7" s="8"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -800,11 +772,10 @@
       <c r="D8" s="2">
         <v>0.44</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="17">
         <v>13.2</v>
       </c>
-      <c r="F8" s="14"/>
-      <c r="G8" s="11"/>
+      <c r="F8" s="8"/>
       <c r="H8" s="8"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -820,11 +791,10 @@
       <c r="D9" s="2">
         <v>0.45</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="17">
         <v>13.4</v>
       </c>
-      <c r="F9" s="14"/>
-      <c r="G9" s="11"/>
+      <c r="F9" s="8"/>
       <c r="H9" s="8"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -840,11 +810,10 @@
       <c r="D10" s="2">
         <v>0.47</v>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="17">
         <v>13.8</v>
       </c>
-      <c r="F10" s="14"/>
-      <c r="G10" s="11"/>
+      <c r="F10" s="8"/>
       <c r="H10" s="8"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -860,11 +829,10 @@
       <c r="D11" s="2">
         <v>0.72</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="17">
         <v>14</v>
       </c>
-      <c r="F11" s="14"/>
-      <c r="G11" s="11"/>
+      <c r="F11" s="8"/>
       <c r="H11" s="8"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -880,11 +848,10 @@
       <c r="D12" s="2">
         <v>0.8</v>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="17">
         <v>14.4</v>
       </c>
-      <c r="F12" s="14"/>
-      <c r="G12" s="11"/>
+      <c r="F12" s="8"/>
       <c r="H12" s="8"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -900,11 +867,10 @@
       <c r="D13" s="2">
         <v>0.51</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="17">
         <v>14</v>
       </c>
-      <c r="F13" s="14"/>
-      <c r="G13" s="11"/>
+      <c r="F13" s="8"/>
       <c r="H13" s="8"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
@@ -920,11 +886,10 @@
       <c r="D14" s="2">
         <v>0.62</v>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="17">
         <v>14</v>
       </c>
-      <c r="F14" s="14"/>
-      <c r="G14" s="11"/>
+      <c r="F14" s="8"/>
       <c r="H14" s="8"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
@@ -940,11 +905,10 @@
       <c r="D15" s="2">
         <v>0.67</v>
       </c>
-      <c r="E15" s="25">
+      <c r="E15" s="17">
         <v>14.1</v>
       </c>
-      <c r="F15" s="14"/>
-      <c r="G15" s="11"/>
+      <c r="F15" s="8"/>
       <c r="H15" s="8"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
@@ -960,11 +924,10 @@
       <c r="D16" s="2">
         <v>0.71</v>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="17">
         <v>15.5</v>
       </c>
-      <c r="F16" s="14"/>
-      <c r="G16" s="11"/>
+      <c r="F16" s="8"/>
       <c r="H16" s="8"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
@@ -980,11 +943,10 @@
       <c r="D17" s="2">
         <v>0.59</v>
       </c>
-      <c r="E17" s="25">
+      <c r="E17" s="17">
         <v>16.899999999999999</v>
       </c>
-      <c r="F17" s="14"/>
-      <c r="G17" s="11"/>
+      <c r="F17" s="8"/>
       <c r="H17" s="8"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
@@ -1000,11 +962,10 @@
       <c r="D18" s="2">
         <v>0.61</v>
       </c>
-      <c r="E18" s="25">
+      <c r="E18" s="17">
         <v>17.399999999999999</v>
       </c>
-      <c r="F18" s="14"/>
-      <c r="G18" s="11"/>
+      <c r="F18" s="8"/>
       <c r="H18" s="8"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
@@ -1020,11 +981,10 @@
       <c r="D19" s="2">
         <v>0.64</v>
       </c>
-      <c r="E19" s="25">
+      <c r="E19" s="17">
         <v>17.8</v>
       </c>
-      <c r="F19" s="14"/>
-      <c r="G19" s="11"/>
+      <c r="F19" s="8"/>
       <c r="H19" s="8"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
@@ -1040,11 +1000,10 @@
       <c r="D20" s="2">
         <v>0.66</v>
       </c>
-      <c r="E20" s="25">
+      <c r="E20" s="17">
         <v>18.2</v>
       </c>
-      <c r="F20" s="14"/>
-      <c r="G20" s="11"/>
+      <c r="F20" s="8"/>
       <c r="H20" s="8"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
@@ -1060,11 +1019,10 @@
       <c r="D21" s="2">
         <v>0.71</v>
       </c>
-      <c r="E21" s="25">
+      <c r="E21" s="17">
         <v>21.5</v>
       </c>
-      <c r="F21" s="14"/>
-      <c r="G21" s="11"/>
+      <c r="F21" s="8"/>
       <c r="H21" s="8"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
@@ -1080,11 +1038,10 @@
       <c r="D22" s="2">
         <v>0.84</v>
       </c>
-      <c r="E22" s="25">
+      <c r="E22" s="17">
         <v>23.4</v>
       </c>
-      <c r="F22" s="14"/>
-      <c r="G22" s="11"/>
+      <c r="F22" s="8"/>
       <c r="H22" s="8"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
@@ -1100,11 +1057,10 @@
       <c r="D23" s="2">
         <v>0.93</v>
       </c>
-      <c r="E23" s="25">
+      <c r="E23" s="17">
         <v>24.1</v>
       </c>
-      <c r="F23" s="14"/>
-      <c r="G23" s="11"/>
+      <c r="F23" s="8"/>
       <c r="H23" s="8"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
@@ -1120,11 +1076,10 @@
       <c r="D24" s="2">
         <v>1.1399999999999999</v>
       </c>
-      <c r="E24" s="25">
+      <c r="E24" s="17">
         <v>23.6</v>
       </c>
-      <c r="F24" s="14"/>
-      <c r="G24" s="11"/>
+      <c r="F24" s="8"/>
       <c r="H24" s="8"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
@@ -1140,11 +1095,10 @@
       <c r="D25" s="2">
         <v>1.47</v>
       </c>
-      <c r="E25" s="25">
+      <c r="E25" s="17">
         <v>25</v>
       </c>
-      <c r="F25" s="14"/>
-      <c r="G25" s="11"/>
+      <c r="F25" s="8"/>
       <c r="H25" s="8"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
@@ -1160,11 +1114,10 @@
       <c r="D26" s="2">
         <v>1.41</v>
       </c>
-      <c r="E26" s="25">
+      <c r="E26" s="17">
         <v>26.5</v>
       </c>
-      <c r="F26" s="14"/>
-      <c r="G26" s="11"/>
+      <c r="F26" s="8"/>
       <c r="H26" s="8"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
@@ -1180,11 +1133,10 @@
       <c r="D27" s="2">
         <v>1.41</v>
       </c>
-      <c r="E27" s="25">
+      <c r="E27" s="17">
         <v>26.7</v>
       </c>
-      <c r="F27" s="14"/>
-      <c r="G27" s="11"/>
+      <c r="F27" s="8"/>
       <c r="H27" s="8"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
@@ -1200,11 +1152,10 @@
       <c r="D28" s="2">
         <v>1.45</v>
       </c>
-      <c r="E28" s="25">
+      <c r="E28" s="17">
         <v>26.9</v>
       </c>
-      <c r="F28" s="14"/>
-      <c r="G28" s="11"/>
+      <c r="F28" s="8"/>
       <c r="H28" s="8"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
@@ -1220,11 +1171,10 @@
       <c r="D29" s="2">
         <v>1.54</v>
       </c>
-      <c r="E29" s="25">
+      <c r="E29" s="17">
         <v>26.7</v>
       </c>
-      <c r="F29" s="14"/>
-      <c r="G29" s="11"/>
+      <c r="F29" s="8"/>
       <c r="H29" s="8"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
@@ -1240,11 +1190,10 @@
       <c r="D30" s="2">
         <v>1.64</v>
       </c>
-      <c r="E30" s="25">
+      <c r="E30" s="17">
         <v>26.8</v>
       </c>
-      <c r="F30" s="14"/>
-      <c r="G30" s="11"/>
+      <c r="F30" s="8"/>
       <c r="H30" s="8"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
@@ -1260,11 +1209,10 @@
       <c r="D31" s="2">
         <v>1.74</v>
       </c>
-      <c r="E31" s="25">
+      <c r="E31" s="17">
         <v>27.6</v>
       </c>
-      <c r="F31" s="14"/>
-      <c r="G31" s="11"/>
+      <c r="F31" s="8"/>
       <c r="H31" s="8"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
@@ -1280,11 +1228,10 @@
       <c r="D32" s="2">
         <v>1.79</v>
       </c>
-      <c r="E32" s="25">
+      <c r="E32" s="17">
         <v>28.4</v>
       </c>
-      <c r="F32" s="14"/>
-      <c r="G32" s="11"/>
+      <c r="F32" s="8"/>
       <c r="H32" s="8"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
@@ -1300,11 +1247,10 @@
       <c r="D33" s="2">
         <v>1.75</v>
       </c>
-      <c r="E33" s="25">
+      <c r="E33" s="17">
         <v>28.9</v>
       </c>
-      <c r="F33" s="14"/>
-      <c r="G33" s="11"/>
+      <c r="F33" s="8"/>
       <c r="H33" s="8"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
@@ -1320,11 +1266,10 @@
       <c r="D34" s="2">
         <v>1.83</v>
       </c>
-      <c r="E34" s="25">
+      <c r="E34" s="17">
         <v>29.4</v>
       </c>
-      <c r="F34" s="14"/>
-      <c r="G34" s="11"/>
+      <c r="F34" s="8"/>
       <c r="H34" s="8"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
@@ -1340,11 +1285,10 @@
       <c r="D35" s="2">
         <v>1.95</v>
       </c>
-      <c r="E35" s="25">
+      <c r="E35" s="17">
         <v>29.8</v>
       </c>
-      <c r="F35" s="14"/>
-      <c r="G35" s="11"/>
+      <c r="F35" s="8"/>
       <c r="H35" s="8"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
@@ -1360,11 +1304,10 @@
       <c r="D36" s="2">
         <v>2.02</v>
       </c>
-      <c r="E36" s="25">
+      <c r="E36" s="17">
         <v>30</v>
       </c>
-      <c r="F36" s="14"/>
-      <c r="G36" s="11"/>
+      <c r="F36" s="8"/>
       <c r="H36" s="8"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
@@ -1380,11 +1323,10 @@
       <c r="D37" s="2">
         <v>2.13</v>
       </c>
-      <c r="E37" s="25">
+      <c r="E37" s="17">
         <v>30.4</v>
       </c>
-      <c r="F37" s="14"/>
-      <c r="G37" s="11"/>
+      <c r="F37" s="8"/>
       <c r="H37" s="8"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
@@ -1400,11 +1342,10 @@
       <c r="D38" s="2">
         <v>2.2799999999999998</v>
       </c>
-      <c r="E38" s="25">
+      <c r="E38" s="17">
         <v>30.9</v>
       </c>
-      <c r="F38" s="14"/>
-      <c r="G38" s="11"/>
+      <c r="F38" s="8"/>
       <c r="H38" s="8"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
@@ -1420,11 +1361,10 @@
       <c r="D39" s="2">
         <v>2.5</v>
       </c>
-      <c r="E39" s="25">
+      <c r="E39" s="17">
         <v>31.2</v>
       </c>
-      <c r="F39" s="14"/>
-      <c r="G39" s="11"/>
+      <c r="F39" s="8"/>
       <c r="H39" s="8"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
@@ -1440,11 +1380,10 @@
       <c r="D40" s="2">
         <v>2.72</v>
       </c>
-      <c r="E40" s="25">
+      <c r="E40" s="17">
         <v>31.8</v>
       </c>
-      <c r="F40" s="14"/>
-      <c r="G40" s="11"/>
+      <c r="F40" s="8"/>
       <c r="H40" s="8"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
@@ -1460,11 +1399,10 @@
       <c r="D41" s="2">
         <v>2.87</v>
       </c>
-      <c r="E41" s="25">
+      <c r="E41" s="17">
         <v>32.9</v>
       </c>
-      <c r="F41" s="14"/>
-      <c r="G41" s="11"/>
+      <c r="F41" s="8"/>
       <c r="H41" s="8"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
@@ -1480,11 +1418,10 @@
       <c r="D42" s="2">
         <v>2.92</v>
       </c>
-      <c r="E42" s="25">
+      <c r="E42" s="17">
         <v>33.9</v>
       </c>
-      <c r="F42" s="14"/>
-      <c r="G42" s="11"/>
+      <c r="F42" s="8"/>
       <c r="H42" s="8"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
@@ -1500,11 +1437,10 @@
       <c r="D43" s="2">
         <v>3.07</v>
       </c>
-      <c r="E43" s="25">
+      <c r="E43" s="17">
         <v>35.5</v>
       </c>
-      <c r="F43" s="14"/>
-      <c r="G43" s="11"/>
+      <c r="F43" s="8"/>
       <c r="H43" s="8"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
@@ -1520,11 +1456,10 @@
       <c r="D44" s="2">
         <v>3.16</v>
       </c>
-      <c r="E44" s="25">
+      <c r="E44" s="17">
         <v>37.700000000000003</v>
       </c>
-      <c r="F44" s="14"/>
-      <c r="G44" s="11"/>
+      <c r="F44" s="8"/>
       <c r="H44" s="8"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
@@ -1540,11 +1475,12 @@
       <c r="D45" s="2">
         <v>3.14</v>
       </c>
-      <c r="E45" s="25">
+      <c r="E45" s="17">
         <v>39.799999999999997</v>
       </c>
-      <c r="F45" s="14"/>
-      <c r="G45" s="11"/>
+      <c r="F45" s="9">
+        <v>-9.9412E-2</v>
+      </c>
       <c r="H45" s="9"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
@@ -1560,11 +1496,12 @@
       <c r="D46" s="2">
         <v>3.07</v>
       </c>
-      <c r="E46" s="25">
+      <c r="E46" s="17">
         <v>41.1</v>
       </c>
-      <c r="F46" s="14"/>
-      <c r="G46" s="11"/>
+      <c r="F46" s="9">
+        <v>0.33241599999999999</v>
+      </c>
       <c r="H46" s="9"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
@@ -1580,11 +1517,12 @@
       <c r="D47" s="2">
         <v>3.15</v>
       </c>
-      <c r="E47" s="25">
+      <c r="E47" s="17">
         <v>42.5</v>
       </c>
-      <c r="F47" s="14"/>
-      <c r="G47" s="12"/>
+      <c r="F47" s="9">
+        <v>0.33558399999999999</v>
+      </c>
       <c r="H47" s="9"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
@@ -1600,10 +1538,12 @@
       <c r="D48" s="2">
         <v>3.38</v>
       </c>
-      <c r="E48" s="25">
+      <c r="E48" s="17">
         <v>46.2</v>
       </c>
-      <c r="F48" s="14"/>
+      <c r="F48" s="9">
+        <v>-0.15588399999999997</v>
+      </c>
       <c r="H48" s="9"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
@@ -1619,10 +1559,12 @@
       <c r="D49" s="2">
         <v>3.6</v>
       </c>
-      <c r="E49" s="25">
+      <c r="E49" s="17">
         <v>51.9</v>
       </c>
-      <c r="F49" s="14"/>
+      <c r="F49" s="9">
+        <v>-0.25567599999999996</v>
+      </c>
       <c r="H49" s="9"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
@@ -1638,10 +1580,12 @@
       <c r="D50" s="2">
         <v>3.68</v>
       </c>
-      <c r="E50" s="25">
+      <c r="E50" s="17">
         <v>55.5</v>
       </c>
-      <c r="F50" s="14"/>
+      <c r="F50" s="9">
+        <v>0.46570400000000001</v>
+      </c>
       <c r="H50" s="9"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
@@ -1657,10 +1601,12 @@
       <c r="D51" s="2">
         <v>4.05</v>
       </c>
-      <c r="E51" s="25">
+      <c r="E51" s="17">
         <v>58.2</v>
       </c>
-      <c r="F51" s="14"/>
+      <c r="F51" s="9">
+        <v>1.7864000000000005E-2</v>
+      </c>
       <c r="H51" s="9"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
@@ -1676,10 +1622,12 @@
       <c r="D52" s="2">
         <v>4.67</v>
       </c>
-      <c r="E52" s="25">
+      <c r="E52" s="17">
         <v>62.1</v>
       </c>
-      <c r="F52" s="14"/>
+      <c r="F52" s="9">
+        <v>0.240892</v>
+      </c>
       <c r="H52" s="9"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
@@ -1695,10 +1643,12 @@
       <c r="D53" s="2">
         <v>5.07</v>
       </c>
-      <c r="E53" s="25">
+      <c r="E53" s="17">
         <v>67.7</v>
       </c>
-      <c r="F53" s="14"/>
+      <c r="F53" s="9">
+        <v>0.31946799999999997</v>
+      </c>
       <c r="H53" s="9"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
@@ -1714,10 +1664,12 @@
       <c r="D54" s="2">
         <v>5.65</v>
       </c>
-      <c r="E54" s="25">
+      <c r="E54" s="17">
         <v>76.7</v>
       </c>
-      <c r="F54" s="14"/>
+      <c r="F54" s="9">
+        <v>8.1108E-2</v>
+      </c>
       <c r="H54" s="9"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
@@ -1733,10 +1685,12 @@
       <c r="D55" s="2">
         <v>6.16</v>
       </c>
-      <c r="E55" s="25">
+      <c r="E55" s="17">
         <v>86.3</v>
       </c>
-      <c r="F55" s="14"/>
+      <c r="F55" s="9">
+        <v>0.26483199999999996</v>
+      </c>
       <c r="H55" s="9"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
@@ -1752,10 +1706,12 @@
       <c r="D56" s="2">
         <v>6.63</v>
       </c>
-      <c r="E56" s="25">
+      <c r="E56" s="17">
         <v>94</v>
       </c>
-      <c r="F56" s="14"/>
+      <c r="F56" s="9">
+        <v>-2.1712000000000002E-2</v>
+      </c>
       <c r="H56" s="9"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
@@ -1771,10 +1727,12 @@
       <c r="D57" s="2">
         <v>6.87</v>
       </c>
-      <c r="E57" s="25">
+      <c r="E57" s="17">
         <v>97.6</v>
       </c>
-      <c r="F57" s="14"/>
+      <c r="F57" s="9">
+        <v>3.6639999999999989E-3</v>
+      </c>
       <c r="H57" s="9"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
@@ -1790,10 +1748,12 @@
       <c r="D58" s="2">
         <v>7.09</v>
       </c>
-      <c r="E58" s="25">
+      <c r="E58" s="17">
         <v>101.3</v>
       </c>
-      <c r="F58" s="14"/>
+      <c r="F58" s="9">
+        <v>0.23741199999999998</v>
+      </c>
       <c r="H58" s="9"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
@@ -1809,10 +1769,12 @@
       <c r="D59" s="2">
         <v>7.53</v>
       </c>
-      <c r="E59" s="25">
+      <c r="E59" s="17">
         <v>105.3</v>
       </c>
-      <c r="F59" s="14"/>
+      <c r="F59" s="9">
+        <v>7.6032000000000002E-2</v>
+      </c>
       <c r="H59" s="9"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
@@ -1828,10 +1790,12 @@
       <c r="D60" s="2">
         <v>7.9</v>
       </c>
-      <c r="E60" s="25">
+      <c r="E60" s="17">
         <v>109.3</v>
       </c>
-      <c r="F60" s="14"/>
+      <c r="F60" s="9">
+        <v>0.56276000000000004</v>
+      </c>
       <c r="H60" s="9"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
@@ -1847,10 +1811,12 @@
       <c r="D61" s="2">
         <v>8.2799999999999994</v>
       </c>
-      <c r="E61" s="25">
+      <c r="E61" s="17">
         <v>110.5</v>
       </c>
-      <c r="F61" s="14"/>
+      <c r="F61" s="9">
+        <v>0.64781200000000005</v>
+      </c>
       <c r="H61" s="9"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
@@ -1866,10 +1832,12 @@
       <c r="D62" s="2">
         <v>8.81</v>
       </c>
-      <c r="E62" s="25">
+      <c r="E62" s="17">
         <v>115.4</v>
       </c>
-      <c r="F62" s="14"/>
+      <c r="F62" s="9">
+        <v>0.261492</v>
+      </c>
       <c r="H62" s="9"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
@@ -1885,10 +1853,15 @@
       <c r="D63" s="2">
         <v>9.75</v>
       </c>
-      <c r="E63" s="25">
+      <c r="E63" s="17">
         <v>120.5</v>
       </c>
-      <c r="F63" s="14"/>
+      <c r="F63" s="9">
+        <v>0.25873199999999996</v>
+      </c>
+      <c r="G63" s="2">
+        <v>0.40429999999999999</v>
+      </c>
       <c r="H63" s="9"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
@@ -1904,10 +1877,15 @@
       <c r="D64" s="2">
         <v>11.06</v>
       </c>
-      <c r="E64" s="25">
+      <c r="E64" s="17">
         <v>126.1</v>
       </c>
-      <c r="F64" s="14"/>
+      <c r="F64" s="9">
+        <v>0.12128400000000002</v>
+      </c>
+      <c r="G64" s="2">
+        <v>0.64959999999999996</v>
+      </c>
       <c r="H64" s="9"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
@@ -1923,10 +1901,15 @@
       <c r="D65" s="2">
         <v>12.09</v>
       </c>
-      <c r="E65" s="25">
+      <c r="E65" s="17">
         <v>133.80000000000001</v>
       </c>
-      <c r="F65" s="14"/>
+      <c r="F65" s="9">
+        <v>-0.19181199999999998</v>
+      </c>
+      <c r="G65" s="2">
+        <v>-0.10550000000000001</v>
+      </c>
       <c r="H65" s="9"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
@@ -1942,10 +1925,15 @@
       <c r="D66" s="2">
         <v>12.2</v>
       </c>
-      <c r="E66" s="25">
+      <c r="E66" s="17">
         <v>137.9</v>
       </c>
-      <c r="F66" s="14"/>
+      <c r="F66" s="9">
+        <v>0.12922400000000001</v>
+      </c>
+      <c r="G66" s="2">
+        <v>0.59909999999999997</v>
+      </c>
       <c r="H66" s="9"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
@@ -1961,10 +1949,15 @@
       <c r="D67" s="2">
         <v>12.39</v>
       </c>
-      <c r="E67" s="25">
+      <c r="E67" s="17">
         <v>141.9</v>
       </c>
-      <c r="F67" s="14"/>
+      <c r="F67" s="9">
+        <v>-0.10865999999999999</v>
+      </c>
+      <c r="G67" s="2">
+        <v>0.114</v>
+      </c>
       <c r="H67" s="9"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
@@ -1980,10 +1973,15 @@
       <c r="D68" s="2">
         <v>12.58</v>
       </c>
-      <c r="E68" s="25">
+      <c r="E68" s="17">
         <v>145.80000000000001</v>
       </c>
-      <c r="F68" s="14"/>
+      <c r="F68" s="9">
+        <v>0.31919999999999998</v>
+      </c>
+      <c r="G68" s="2">
+        <v>0.74840000000000007</v>
+      </c>
       <c r="H68" s="9"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
@@ -1999,10 +1997,15 @@
       <c r="D69" s="2">
         <v>13.17</v>
       </c>
-      <c r="E69" s="25">
+      <c r="E69" s="17">
         <v>149.69999999999999</v>
       </c>
-      <c r="F69" s="14"/>
+      <c r="F69" s="9">
+        <v>6.8972000000000006E-2</v>
+      </c>
+      <c r="G69" s="2">
+        <v>-7.3200000000000001E-2</v>
+      </c>
       <c r="H69" s="9"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
@@ -2018,10 +2021,15 @@
       <c r="D70" s="2">
         <v>13.79</v>
       </c>
-      <c r="E70" s="25">
+      <c r="E70" s="17">
         <v>153.5</v>
       </c>
-      <c r="F70" s="14"/>
+      <c r="F70" s="9">
+        <v>0.127164</v>
+      </c>
+      <c r="G70" s="2">
+        <v>-5.21E-2</v>
+      </c>
       <c r="H70" s="9"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
@@ -2037,10 +2045,15 @@
       <c r="D71" s="2">
         <v>14.9</v>
       </c>
-      <c r="E71" s="25">
+      <c r="E71" s="17">
         <v>158.6</v>
       </c>
-      <c r="F71" s="14"/>
+      <c r="F71" s="9">
+        <v>8.8872000000000007E-2</v>
+      </c>
+      <c r="G71" s="2">
+        <v>6.0299999999999999E-2</v>
+      </c>
       <c r="H71" s="9"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
@@ -2056,10 +2069,15 @@
       <c r="D72" s="2">
         <v>15.5</v>
       </c>
-      <c r="E72" s="25">
+      <c r="E72" s="17">
         <v>161.30000000000001</v>
       </c>
-      <c r="F72" s="14"/>
+      <c r="F72" s="9">
+        <v>4.5272000000000007E-2</v>
+      </c>
+      <c r="G72" s="2">
+        <v>-0.1159</v>
+      </c>
       <c r="H72" s="9"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
@@ -2075,10 +2093,15 @@
       <c r="D73" s="2">
         <v>16.2</v>
       </c>
-      <c r="E73" s="25">
+      <c r="E73" s="17">
         <v>163.9</v>
       </c>
-      <c r="F73" s="14"/>
+      <c r="F73" s="9">
+        <v>0.20026399999999997</v>
+      </c>
+      <c r="G73" s="2">
+        <v>-0.25340000000000001</v>
+      </c>
       <c r="H73" s="9"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
@@ -2094,10 +2117,15 @@
       <c r="D74" s="2">
         <v>16.690000000000001</v>
       </c>
-      <c r="E74" s="25">
+      <c r="E74" s="17">
         <v>168.3</v>
       </c>
-      <c r="F74" s="14"/>
+      <c r="F74" s="9">
+        <v>0.25518000000000002</v>
+      </c>
+      <c r="G74" s="2">
+        <v>0.66409999999999991</v>
+      </c>
       <c r="H74" s="9"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
@@ -2113,10 +2141,15 @@
       <c r="D75" s="2">
         <v>16.27</v>
       </c>
-      <c r="E75" s="25">
+      <c r="E75" s="17">
         <v>174</v>
       </c>
-      <c r="F75" s="14"/>
+      <c r="F75" s="9">
+        <v>-0.136684</v>
+      </c>
+      <c r="G75" s="2">
+        <v>-0.30609999999999998</v>
+      </c>
       <c r="H75" s="9"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
@@ -2132,10 +2165,15 @@
       <c r="D76" s="2">
         <v>15.74</v>
       </c>
-      <c r="E76" s="25">
+      <c r="E76" s="17">
         <v>176.7</v>
       </c>
-      <c r="F76" s="14"/>
+      <c r="F76" s="9">
+        <v>-0.20350800000000002</v>
+      </c>
+      <c r="G76" s="2">
+        <v>-2.3700000000000002E-2</v>
+      </c>
       <c r="H76" s="9"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
@@ -2151,10 +2189,15 @@
       <c r="D77" s="2">
         <v>16.07</v>
       </c>
-      <c r="E77" s="25">
+      <c r="E77" s="17">
         <v>180.9</v>
       </c>
-      <c r="F77" s="14"/>
+      <c r="F77" s="9">
+        <v>-0.15608399999999997</v>
+      </c>
+      <c r="G77" s="2">
+        <v>-0.06</v>
+      </c>
       <c r="H77" s="9"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
@@ -2170,10 +2213,15 @@
       <c r="D78" s="2">
         <v>17.39</v>
       </c>
-      <c r="E78" s="25">
+      <c r="E78" s="17">
         <v>184.3</v>
       </c>
-      <c r="F78" s="14"/>
+      <c r="F78" s="9">
+        <v>0.38316800000000001</v>
+      </c>
+      <c r="G78" s="2">
+        <v>0.56279999999999997</v>
+      </c>
       <c r="H78" s="9"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
@@ -2189,10 +2237,15 @@
       <c r="D79" s="2">
         <v>19.440000000000001</v>
       </c>
-      <c r="E79" s="25">
+      <c r="E79" s="17">
         <v>190.3</v>
       </c>
-      <c r="F79" s="14"/>
+      <c r="F79" s="9">
+        <v>0.20564399999999999</v>
+      </c>
+      <c r="G79" s="2">
+        <v>0.25950000000000001</v>
+      </c>
       <c r="H79" s="9"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
@@ -2208,10 +2261,15 @@
       <c r="D80" s="2">
         <v>22.22</v>
       </c>
-      <c r="E80" s="25">
+      <c r="E80" s="17">
         <v>196.8</v>
       </c>
-      <c r="F80" s="14"/>
+      <c r="F80" s="9">
+        <v>0.13223199999999999</v>
+      </c>
+      <c r="G80" s="2">
+        <v>0.34539999999999998</v>
+      </c>
       <c r="H80" s="9"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
@@ -2227,10 +2285,15 @@
       <c r="D81" s="2">
         <v>24.88</v>
       </c>
-      <c r="E81" s="25">
+      <c r="E81" s="17">
         <v>201.8</v>
       </c>
-      <c r="F81" s="14"/>
+      <c r="F81" s="9">
+        <v>0.27316000000000001</v>
+      </c>
+      <c r="G81" s="2">
+        <v>0.32549999999999996</v>
+      </c>
       <c r="H81" s="9"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
@@ -2246,10 +2309,15 @@
       <c r="D82" s="2">
         <v>27.73</v>
       </c>
-      <c r="E82" s="25">
+      <c r="E82" s="17">
         <v>210.036</v>
       </c>
-      <c r="F82" s="14"/>
+      <c r="F82" s="9">
+        <v>0.11241200000000001</v>
+      </c>
+      <c r="G82" s="2">
+        <v>0.3982</v>
+      </c>
       <c r="H82" s="9"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
@@ -2265,10 +2333,15 @@
       <c r="D83" s="2">
         <v>28.39</v>
       </c>
-      <c r="E83" s="25">
+      <c r="E83" s="17">
         <v>210.22800000000001</v>
       </c>
-      <c r="F83" s="14"/>
+      <c r="F83" s="9">
+        <v>-0.43691200000000002</v>
+      </c>
+      <c r="G83" s="2">
+        <v>-0.53180000000000005</v>
+      </c>
       <c r="H83" s="9"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
@@ -2284,10 +2357,15 @@
       <c r="D84" s="2">
         <v>22.41</v>
       </c>
-      <c r="E84" s="25">
+      <c r="E84" s="17">
         <v>215.94900000000001</v>
       </c>
-      <c r="F84" s="14"/>
+      <c r="F84" s="9">
+        <v>0.33769199999999999</v>
+      </c>
+      <c r="G84" s="2">
+        <v>0.79020000000000001</v>
+      </c>
       <c r="H84" s="9"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
@@ -2303,10 +2381,15 @@
       <c r="D85" s="2">
         <v>22.73</v>
       </c>
-      <c r="E85" s="25">
+      <c r="E85" s="17">
         <v>219.179</v>
       </c>
-      <c r="F85" s="14"/>
+      <c r="F85" s="9">
+        <v>8.2808000000000007E-2</v>
+      </c>
+      <c r="G85" s="2">
+        <v>0.192</v>
+      </c>
       <c r="H85" s="9"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
@@ -2322,10 +2405,15 @@
       <c r="D86" s="2">
         <v>26.43</v>
       </c>
-      <c r="E86" s="25">
+      <c r="E86" s="17">
         <v>225.672</v>
       </c>
-      <c r="F86" s="14"/>
+      <c r="F86" s="9">
+        <v>-0.106248</v>
+      </c>
+      <c r="G86" s="2">
+        <v>-0.18170000000000003</v>
+      </c>
       <c r="H86" s="9"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
@@ -2341,10 +2429,15 @@
       <c r="D87" s="2">
         <v>31.25</v>
       </c>
-      <c r="E87" s="25">
+      <c r="E87" s="17">
         <v>229.601</v>
       </c>
-      <c r="F87" s="14"/>
+      <c r="F87" s="9">
+        <v>0.17587999999999998</v>
+      </c>
+      <c r="G87" s="2">
+        <v>0.18629999999999999</v>
+      </c>
       <c r="H87" s="9"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
@@ -2360,10 +2453,15 @@
       <c r="D88" s="2">
         <v>34.99</v>
       </c>
-      <c r="E88" s="25">
+      <c r="E88" s="17">
         <v>233.04900000000001</v>
       </c>
-      <c r="F88" s="14"/>
+      <c r="F88" s="9">
+        <v>0.22980400000000001</v>
+      </c>
+      <c r="G88" s="2">
+        <v>-2.2700000000000001E-2</v>
+      </c>
       <c r="H88" s="9"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
@@ -2379,10 +2477,15 @@
       <c r="D89" s="2">
         <v>39.44</v>
       </c>
-      <c r="E89" s="25">
+      <c r="E89" s="17">
         <v>234.81200000000001</v>
       </c>
-      <c r="F89" s="14"/>
+      <c r="F89" s="9">
+        <v>-4.584400000000001E-2</v>
+      </c>
+      <c r="G89" s="2">
+        <v>-1.8200000000000001E-2</v>
+      </c>
       <c r="H89" s="9"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
@@ -2398,10 +2501,15 @@
       <c r="D90" s="2">
         <v>43.39</v>
       </c>
-      <c r="E90" s="25">
+      <c r="E90" s="17">
         <v>236.52500000000001</v>
       </c>
-      <c r="F90" s="14"/>
+      <c r="F90" s="9">
+        <v>-1.2444E-2</v>
+      </c>
+      <c r="G90" s="2">
+        <v>-0.14599999999999999</v>
+      </c>
       <c r="H90" s="9"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
@@ -2417,10 +2525,15 @@
       <c r="D91" s="2">
         <v>45.7</v>
       </c>
-      <c r="E91" s="25">
+      <c r="E91" s="17">
         <v>241.43199999999999</v>
       </c>
-      <c r="F91" s="14"/>
+      <c r="F91" s="9">
+        <v>1.3240000000000002E-2</v>
+      </c>
+      <c r="G91" s="2">
+        <v>0.11599999999999999</v>
+      </c>
       <c r="H91" s="9"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
@@ -2436,10 +2549,15 @@
       <c r="D92" s="2">
         <v>48.93</v>
       </c>
-      <c r="E92" s="25">
+      <c r="E92" s="17">
         <v>246.524</v>
       </c>
-      <c r="F92" s="14"/>
+      <c r="F92" s="9">
+        <v>0.25231199999999998</v>
+      </c>
+      <c r="G92" s="2">
+        <v>0.3775</v>
+      </c>
       <c r="H92" s="9"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
@@ -2455,10 +2573,15 @@
       <c r="D93" s="2">
         <v>53.75</v>
       </c>
-      <c r="E93" s="25">
+      <c r="E93" s="17">
         <v>251.233</v>
       </c>
-      <c r="F93" s="14"/>
+      <c r="F93" s="9">
+        <v>-0.134488</v>
+      </c>
+      <c r="G93" s="2">
+        <v>-0.14249999999999999</v>
+      </c>
       <c r="H93" s="9"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
@@ -2474,10 +2597,15 @@
       <c r="D94" s="2">
         <v>58.24</v>
       </c>
-      <c r="E94" s="25">
+      <c r="E94" s="17">
         <v>256.97399999999999</v>
       </c>
-      <c r="F94" s="14"/>
+      <c r="F94" s="9">
+        <v>0.22476399999999999</v>
+      </c>
+      <c r="G94" s="2">
+        <v>0.1888</v>
+      </c>
       <c r="H94" s="9"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
@@ -2493,10 +2621,15 @@
       <c r="D95" s="2">
         <v>58.28</v>
       </c>
-      <c r="E95" s="25">
+      <c r="E95" s="17">
         <v>260.47399999999999</v>
       </c>
-      <c r="F95" s="14"/>
+      <c r="F95" s="9">
+        <v>6.0347999999999999E-2</v>
+      </c>
+      <c r="G95" s="2">
+        <v>0.18690000000000001</v>
+      </c>
       <c r="H95" s="9"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
@@ -2512,10 +2645,15 @@
       <c r="D96" s="2">
         <v>60.91</v>
       </c>
-      <c r="E96" s="25">
+      <c r="E96" s="17">
         <v>278.80200000000002</v>
       </c>
-      <c r="F96" s="14"/>
+      <c r="F96" s="9">
+        <v>0.12589999999999998</v>
+      </c>
+      <c r="G96" s="2">
+        <v>-2.2200000000000001E-2</v>
+      </c>
       <c r="H96" s="9"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
@@ -2531,10 +2669,15 @@
       <c r="D97" s="2">
         <v>66.92</v>
       </c>
-      <c r="E97" s="25">
+      <c r="E97" s="17">
         <v>296.79700000000003</v>
       </c>
-      <c r="F97" s="14"/>
+      <c r="F97" s="9">
+        <v>-0.129084</v>
+      </c>
+      <c r="G97" s="2">
+        <v>-0.19739999999999999</v>
+      </c>
       <c r="H97" s="9"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
@@ -2550,10 +2693,15 @@
       <c r="D98" s="2">
         <v>70.3</v>
       </c>
-      <c r="E98" s="25">
+      <c r="E98" s="17">
         <v>306.74599999999998</v>
       </c>
-      <c r="F98" s="14"/>
+      <c r="F98" s="9">
+        <v>0.182812</v>
+      </c>
+      <c r="G98" s="2">
+        <v>0.1027</v>
+      </c>
       <c r="H98" s="9"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
@@ -2569,10 +2717,15 @@
       <c r="D99" s="2">
         <v>74.83</v>
       </c>
-      <c r="E99" s="25">
+      <c r="E99" s="17">
         <v>315.60500000000002</v>
       </c>
-      <c r="F99" s="14"/>
+      <c r="F99" s="9">
+        <v>4.7339999999999993E-2</v>
+      </c>
+      <c r="G99" s="2">
+        <v>8.0500000000000002E-2</v>
+      </c>
       <c r="H99" s="9"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
@@ -2588,7 +2741,12 @@
       <c r="D100" s="6">
         <v>78.92</v>
       </c>
-      <c r="F100" s="14"/>
+      <c r="F100" s="9">
+        <v>0.32277600000000001</v>
+      </c>
+      <c r="G100" s="2">
+        <v>0.34360000000000002</v>
+      </c>
       <c r="H100" s="9"/>
     </row>
   </sheetData>
@@ -2605,133 +2763,157 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.28515625" style="17" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" style="17" customWidth="1"/>
-    <col min="3" max="3" width="33.5703125" style="18" customWidth="1"/>
-    <col min="4" max="4" width="28.7109375" style="17" customWidth="1"/>
-    <col min="5" max="5" width="36.140625" style="17" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="17"/>
+    <col min="1" max="1" width="29.28515625" style="11" customWidth="1"/>
+    <col min="2" max="2" width="36.28515625" style="11" customWidth="1"/>
+    <col min="3" max="3" width="33.5703125" style="12" customWidth="1"/>
+    <col min="4" max="4" width="28.7109375" style="11" customWidth="1"/>
+    <col min="5" max="5" width="36.140625" style="11" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="27" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:5" s="19" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="18" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="28" t="s">
+    <row r="2" spans="1:5" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="28" t="s">
+      <c r="D2" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="22" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="27" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A3" s="26" t="s">
+    <row r="3" spans="1:5" s="19" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="D3" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="E3" s="18" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
+    <row r="4" spans="1:5" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="E4" s="18" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:5" s="27" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A5" s="26" t="s">
+    <row r="5" spans="1:5" s="19" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A5" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="E5" s="18" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:5" s="27" customFormat="1" ht="54" x14ac:dyDescent="0.25">
-      <c r="A6" s="26" t="s">
+    <row r="6" spans="1:5" s="19" customFormat="1" ht="54" x14ac:dyDescent="0.25">
+      <c r="A6" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="31" t="s">
+      <c r="C6" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="D6" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="26" t="s">
+      <c r="E6" s="18" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D7" s="19"/>
-      <c r="E7" s="23"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="20"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="24"/>
+    <row r="7" spans="1:5" s="13" customFormat="1" ht="72" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="13" customFormat="1" ht="72" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="22"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="24"/>
+      <c r="A9" s="15"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="16"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/bayes-yjx.xlsx
+++ b/bayes-yjx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansa1\OneDrive\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C3410E3-C427-4B2F-9D6D-71B39AC7E667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD3B79F-AC0C-4901-8A0C-9E4D2AC416AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -2741,6 +2741,9 @@
       <c r="D100" s="6">
         <v>78.92</v>
       </c>
+      <c r="E100" s="2">
+        <v>324.05399999999997</v>
+      </c>
       <c r="F100" s="9">
         <v>0.32277600000000001</v>
       </c>
